--- a/artfynd/A 17465-2026 artfynd.xlsx
+++ b/artfynd/A 17465-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,6 +1157,213 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133373782</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96716</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Söder om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>567932</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6505558</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133373663</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57954</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Söder om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567843</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6505522</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17465-2026 artfynd.xlsx
+++ b/artfynd/A 17465-2026 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>133373782</v>
       </c>
       <c r="B6" t="n">
-        <v>96716</v>
+        <v>96718</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>133373663</v>
       </c>
       <c r="B7" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 17465-2026 artfynd.xlsx
+++ b/artfynd/A 17465-2026 artfynd.xlsx
@@ -675,66 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120821305</v>
+        <v>121348102</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mossen OSO 805 m, Ög</t>
+          <t>Torshags skjutbana markörgraven N 130 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567839</v>
+        <v>567902</v>
       </c>
       <c r="R2" t="n">
-        <v>6505520</v>
+        <v>6505444</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,69 +782,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120821257</v>
+        <v>133373782</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossen OSO-O 820 m, Ög</t>
+          <t>Söder om Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567867</v>
+        <v>567932</v>
       </c>
       <c r="R3" t="n">
-        <v>6505580</v>
+        <v>6505558</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,35 +869,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121348102</v>
+        <v>133373663</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,41 +895,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Torshags skjutbana markörgraven N 130 m, Ög</t>
+          <t>Söder om Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567902</v>
+        <v>567843</v>
       </c>
       <c r="R4" t="n">
-        <v>6505444</v>
+        <v>6505522</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,90 +971,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121746538</v>
+        <v>120821257</v>
       </c>
       <c r="B5" t="n">
-        <v>105262</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mossen OSO-O 810 m, Ög</t>
+          <t>Mossen OSO-O 820 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567862</v>
+        <v>567867</v>
       </c>
       <c r="R5" t="n">
-        <v>6505607</v>
+        <v>6505580</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1121,12 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,9 +1088,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gles barrskog med björkinslag</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1159,52 +1108,64 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133373782</v>
+        <v>120821305</v>
       </c>
       <c r="B6" t="n">
-        <v>96766</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söder om Södra Granstorp, Ög</t>
+          <t>Mossen OSO 805 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567932</v>
+        <v>567839</v>
       </c>
       <c r="R6" t="n">
-        <v>6505558</v>
+        <v>6505520</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,71 +1207,84 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133373663</v>
+        <v>121746538</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>106244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söder om Södra Granstorp, Ög</t>
+          <t>Mossen OSO-O 810 m, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567843</v>
+        <v>567862</v>
       </c>
       <c r="R7" t="n">
-        <v>6505522</v>
+        <v>6505607</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,12 +1308,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,18 +1322,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gles barrskog med björkinslag</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 17465-2026 artfynd.xlsx
+++ b/artfynd/A 17465-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121348102</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133373782</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133373663</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120821257</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120821305</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,8 +1373,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121746538</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>